--- a/temasTiempo.xlsx
+++ b/temasTiempo.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\GITHUB\trabajocientifico\curso_machine_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF11CE1F-8F4A-47DF-8DB1-205B1AD388B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7583D62-EA97-4523-97E7-92F1B2413DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Conceptos</t>
   </si>
@@ -33,33 +44,9 @@
     <t>Instalación</t>
   </si>
   <si>
-    <t>Regresión líneal</t>
-  </si>
-  <si>
-    <t>Regresión logistica</t>
-  </si>
-  <si>
-    <t>Arbol de decisión</t>
-  </si>
-  <si>
-    <t>Random Forest</t>
-  </si>
-  <si>
     <t>Gradiente boosting</t>
   </si>
   <si>
-    <t>K vecinos más cercanos</t>
-  </si>
-  <si>
-    <t>Maquinas de soporte vectorial</t>
-  </si>
-  <si>
-    <t>Kmeans</t>
-  </si>
-  <si>
-    <t>Análisis de componentes principales</t>
-  </si>
-  <si>
     <t>Ingeniería de caracteristicas</t>
   </si>
   <si>
@@ -69,15 +56,41 @@
     <t>Horas</t>
   </si>
   <si>
-    <t>Redes neurales</t>
+    <t>Regresión líneal y Regresión logística</t>
+  </si>
+  <si>
+    <t>Arbol de decisión y Random Forest</t>
+  </si>
+  <si>
+    <t>K vecinos más cercanos  y Maquinas de soporte vectorial</t>
+  </si>
+  <si>
+    <t>Kmeans y Analisis Componentes Principales</t>
+  </si>
+  <si>
+    <t>Redes neurales y Deep Learning</t>
+  </si>
+  <si>
+    <t>Anomalias y series de tiempo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -105,8 +118,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,122 +408,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="1">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" s="1">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
+      <c r="B13" s="2">
         <v>4</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46326</v>
       </c>
     </row>
   </sheetData>
